--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_灵魂配置表_Manufacture_SoulConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_灵魂配置表_Manufacture_SoulConfig.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -891,9 +891,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1342,10 +1345,10 @@
       <c r="F4" t="s">
         <v>28</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>5</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>5</v>
       </c>
     </row>
@@ -1368,10 +1371,10 @@
       <c r="F5" t="s">
         <v>28</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="2" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1394,10 +1397,10 @@
       <c r="F6" t="s">
         <v>39</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1420,10 +1423,10 @@
       <c r="F7" t="s">
         <v>46</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="2" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1446,10 +1449,10 @@
       <c r="F8" t="s">
         <v>28</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="2" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1472,10 +1475,10 @@
       <c r="F9" t="s">
         <v>39</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="2" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1498,10 +1501,10 @@
       <c r="F10" t="s">
         <v>46</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="2" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1524,10 +1527,10 @@
       <c r="F11" t="s">
         <v>28</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1550,10 +1553,10 @@
       <c r="F12" t="s">
         <v>39</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1576,10 +1579,10 @@
       <c r="F13" t="s">
         <v>46</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="2" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1602,10 +1605,10 @@
       <c r="F14" t="s">
         <v>28</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="2" t="s">
         <v>79</v>
       </c>
     </row>
